--- a/public/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/01_영업인지/프로젝트명_실행예산서_V1.0_20230531.xlsx
+++ b/public/templates/000_pm_suite/02_프로젝트 개발/01_컨설팅/01_영업인지/프로젝트명_실행예산서_V1.0_20230531.xlsx
@@ -532,7 +532,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-27] SyncGuard AI 프로젝트 수행 실행예산서 (Working Budget &amp; P&amp;L) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-27] SyncFlow AI 프로젝트 수행 실행예산서 (Working Budget &amp; P&amp;L) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>세부 비목 및 산출 내역 (SyncGuard AI 기준)</t>
+          <t>세부 비목 및 산출 내역 (SyncFlow AI 기준)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>SyncGuard AI 구축 용역 총 계약금액 (VAT 별도 공급가액)</t>
+          <t>SyncFlow AI 구축 용역 총 계약금액 (VAT 별도 공급가액)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
